--- a/image source/teeth_brushing_record.xlsx
+++ b/image source/teeth_brushing_record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Desktop\Project\kinder-track\image source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA6CEE0-2663-4DAF-A2A6-952D1C893398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793B66B8-CFC7-4507-85C3-8CB3EA219BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บันทึกการแปรงฟัน" sheetId="1" r:id="rId1"/>
@@ -469,14 +469,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -484,15 +478,21 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -810,7 +810,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31"/>
@@ -888,10 +888,10 @@
       <c r="AI2" s="31"/>
     </row>
     <row r="3" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="37" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2">
@@ -987,10 +987,10 @@
       <c r="AG3" s="6">
         <v>31</v>
       </c>
-      <c r="AH3" s="39" t="s">
+      <c r="AH3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="AI3" s="34" t="s">
+      <c r="AI3" s="37" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       <c r="AI44" s="17"/>
     </row>
     <row r="45" spans="1:35" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="38" t="s">
+      <c r="A45" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B45" s="35"/>
@@ -2909,7 +2909,7 @@
       <c r="AI45" s="20"/>
     </row>
     <row r="47" spans="1:35" ht="25.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="38" t="s">
         <v>14</v>
       </c>
       <c r="B47" s="31"/>
@@ -2924,7 +2924,7 @@
       <c r="K47" s="31"/>
       <c r="L47" s="31"/>
       <c r="M47" s="31"/>
-      <c r="S47" s="40" t="s">
+      <c r="S47" s="38" t="s">
         <v>15</v>
       </c>
       <c r="T47" s="31"/>
@@ -2945,7 +2945,7 @@
       <c r="AI47" s="31"/>
     </row>
     <row r="49" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="39" t="s">
         <v>16</v>
       </c>
       <c r="B49" s="31"/>
@@ -2953,7 +2953,7 @@
       <c r="D49" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="33" t="e">
+      <c r="E49" s="40" t="e">
         <f>แปรงฟัน (มาโรงเรียน)</f>
         <v>#NAME?</v>
       </c>
@@ -2964,7 +2964,7 @@
       <c r="K49" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="L49" s="33" t="e">
+      <c r="L49" s="40" t="e">
         <f>ขาด / ไม่ได้แปรงฟัน</f>
         <v>#NAME?</v>
       </c>
@@ -2973,7 +2973,7 @@
       <c r="O49" s="31"/>
       <c r="P49" s="31"/>
       <c r="R49" s="23"/>
-      <c r="S49" s="33" t="e">
+      <c r="S49" s="40" t="e">
         <f>วันหยุด / ไม่มีข้อมูล</f>
         <v>#NAME?</v>
       </c>
@@ -2984,6 +2984,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="S49:W49"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="E49:I49"/>
+    <mergeCell ref="L49:P49"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="AH3:AH4"/>
@@ -2991,12 +2997,6 @@
     <mergeCell ref="S47:AI47"/>
     <mergeCell ref="A47:M47"/>
     <mergeCell ref="A2:AI2"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="S49:W49"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="E49:I49"/>
-    <mergeCell ref="L49:P49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="81" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -3019,7 +3019,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="31"/>
@@ -3041,7 +3041,7 @@
       <c r="R1" s="31"/>
     </row>
     <row r="2" spans="1:18" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="31"/>
@@ -5305,7 +5305,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="32" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="31"/>
